--- a/food/饭店评分.xlsx
+++ b/food/饭店评分.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ROG\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD426A3F-261E-40D2-9198-42B8A513DC1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7153EB79-2B04-4081-A2B3-F6A8750FB50B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5629,7 +5629,7 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>肠粉</t>
+    <t>肠粉，梅州腌面</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -6518,114 +6518,117 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="2">
+        <v>2026</v>
+      </c>
       <c r="B13" s="2">
         <v>12</v>
       </c>
       <c r="C13" s="7">
-        <v>83.9</v>
+        <v>84.5</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>39</v>
+        <v>1701</v>
       </c>
       <c r="E13" s="7">
-        <v>83</v>
-      </c>
-      <c r="F13" s="5">
-        <v>94</v>
-      </c>
-      <c r="G13" s="5">
-        <v>90</v>
+        <v>82</v>
+      </c>
+      <c r="F13" s="8">
+        <v>60</v>
+      </c>
+      <c r="G13" s="2">
+        <v>46</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>40</v>
+        <v>1702</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>42</v>
+        <v>1711</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>43</v>
+        <v>1713</v>
       </c>
       <c r="L13" s="2">
         <f>(SUM(7*E13,G13,2*F13))/10</f>
-        <v>85.9</v>
+        <v>74</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="2">
-        <v>2026</v>
-      </c>
       <c r="B14" s="2">
         <v>13</v>
       </c>
       <c r="C14" s="7">
         <v>83.9</v>
       </c>
-      <c r="D14" s="12" t="s">
-        <v>1262</v>
+      <c r="D14" s="2" t="s">
+        <v>39</v>
       </c>
       <c r="E14" s="7">
-        <v>82</v>
-      </c>
-      <c r="F14" s="8">
-        <v>65</v>
-      </c>
-      <c r="G14" s="8">
-        <v>60</v>
-      </c>
-      <c r="H14" s="12" t="s">
-        <v>1264</v>
-      </c>
-      <c r="I14" s="12" t="s">
-        <v>1267</v>
-      </c>
-      <c r="J14" s="13" t="s">
-        <v>1271</v>
-      </c>
-      <c r="K14" s="12" t="s">
-        <v>1276</v>
+        <v>83</v>
+      </c>
+      <c r="F14" s="5">
+        <v>94</v>
+      </c>
+      <c r="G14" s="5">
+        <v>90</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="L14" s="2">
         <f>(SUM(7*E14,G14,2*F14))/10</f>
-        <v>76.400000000000006</v>
+        <v>85.9</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="2">
+        <v>2026</v>
+      </c>
       <c r="B15" s="2">
         <v>14</v>
       </c>
       <c r="C15" s="7">
         <v>83.9</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>63</v>
+      <c r="D15" s="12" t="s">
+        <v>1262</v>
       </c>
       <c r="E15" s="7">
-        <v>84</v>
-      </c>
-      <c r="F15" s="7">
-        <v>83</v>
-      </c>
-      <c r="G15" s="7">
-        <v>85</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J15" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="F15" s="8">
         <v>65</v>
       </c>
-      <c r="K15" s="2" t="s">
-        <v>66</v>
+      <c r="G15" s="8">
+        <v>60</v>
+      </c>
+      <c r="H15" s="12" t="s">
+        <v>1264</v>
+      </c>
+      <c r="I15" s="12" t="s">
+        <v>1267</v>
+      </c>
+      <c r="J15" s="13" t="s">
+        <v>1271</v>
+      </c>
+      <c r="K15" s="12" t="s">
+        <v>1276</v>
       </c>
       <c r="L15" s="2">
         <f>(SUM(7*E15,G15,2*F15))/10</f>
-        <v>83.9</v>
+        <v>76.400000000000006</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -6633,74 +6636,71 @@
         <v>15</v>
       </c>
       <c r="C16" s="7">
-        <v>83.6</v>
+        <v>83.9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="E16" s="10">
-        <v>75</v>
+        <v>63</v>
+      </c>
+      <c r="E16" s="7">
+        <v>84</v>
       </c>
       <c r="F16" s="7">
-        <v>89</v>
-      </c>
-      <c r="G16" s="8">
-        <v>68</v>
+        <v>83</v>
+      </c>
+      <c r="G16" s="7">
+        <v>85</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>72</v>
+        <v>13</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="L16" s="2">
         <f>(SUM(7*E16,G16,2*F16))/10</f>
-        <v>77.099999999999994</v>
+        <v>83.9</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="2">
-        <v>2026</v>
-      </c>
       <c r="B17" s="2">
         <v>16</v>
       </c>
       <c r="C17" s="7">
-        <v>83.5</v>
+        <v>83.6</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>1701</v>
-      </c>
-      <c r="E17" s="7">
-        <v>82</v>
-      </c>
-      <c r="F17" s="8">
-        <v>60</v>
-      </c>
-      <c r="G17" s="2">
-        <v>46</v>
+        <v>70</v>
+      </c>
+      <c r="E17" s="10">
+        <v>75</v>
+      </c>
+      <c r="F17" s="7">
+        <v>89</v>
+      </c>
+      <c r="G17" s="8">
+        <v>68</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>1702</v>
+        <v>71</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>1711</v>
+        <v>23</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>1713</v>
+        <v>73</v>
       </c>
       <c r="L17" s="2">
         <f>(SUM(7*E17,G17,2*F17))/10</f>
-        <v>74</v>
+        <v>77.099999999999994</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -11459,45 +11459,45 @@
       </c>
     </row>
     <row r="150" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A150" s="2">
+        <v>2026</v>
+      </c>
       <c r="B150" s="2">
         <v>149</v>
       </c>
       <c r="C150" s="6">
-        <v>74.400000000000006</v>
-      </c>
-      <c r="D150" s="2" t="s">
-        <v>270</v>
+        <v>74.5</v>
+      </c>
+      <c r="D150" s="12" t="s">
+        <v>1322</v>
       </c>
       <c r="E150" s="6">
-        <v>78</v>
-      </c>
-      <c r="F150" s="8">
-        <v>61</v>
+        <v>75</v>
+      </c>
+      <c r="F150" s="2">
+        <v>58</v>
       </c>
       <c r="G150" s="2">
-        <v>56</v>
-      </c>
-      <c r="H150" s="2" t="s">
-        <v>85</v>
+        <v>44</v>
+      </c>
+      <c r="H150" s="12" t="s">
+        <v>1264</v>
       </c>
       <c r="I150" s="2" t="s">
         <v>36</v>
       </c>
       <c r="J150" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="K150" s="2" t="s">
-        <v>271</v>
+        <v>132</v>
+      </c>
+      <c r="K150" s="12" t="s">
+        <v>1326</v>
       </c>
       <c r="L150" s="2">
         <f>(SUM(7*E150,G150,2*F150))/10</f>
-        <v>72.400000000000006</v>
+        <v>68.5</v>
       </c>
     </row>
     <row r="151" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A151" s="2">
-        <v>2026</v>
-      </c>
       <c r="B151" s="2">
         <v>150</v>
       </c>
@@ -11505,65 +11505,68 @@
         <v>74.400000000000006</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>1651</v>
+        <v>270</v>
       </c>
       <c r="E151" s="6">
-        <v>76</v>
-      </c>
-      <c r="F151" s="6">
-        <v>77</v>
-      </c>
-      <c r="G151" s="8">
-        <v>68</v>
+        <v>78</v>
+      </c>
+      <c r="F151" s="8">
+        <v>61</v>
+      </c>
+      <c r="G151" s="2">
+        <v>56</v>
       </c>
       <c r="H151" s="2" t="s">
-        <v>1653</v>
+        <v>85</v>
       </c>
       <c r="I151" s="2" t="s">
-        <v>1662</v>
+        <v>36</v>
       </c>
       <c r="J151" s="3" t="s">
-        <v>1669</v>
+        <v>140</v>
+      </c>
+      <c r="K151" s="2" t="s">
+        <v>271</v>
       </c>
       <c r="L151" s="2">
         <f>(SUM(7*E151,G151,2*F151))/10</f>
-        <v>75.400000000000006</v>
+        <v>72.400000000000006</v>
       </c>
     </row>
     <row r="152" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A152" s="2">
+        <v>2026</v>
+      </c>
       <c r="B152" s="2">
         <v>151</v>
       </c>
       <c r="C152" s="6">
-        <v>74.3</v>
+        <v>74.400000000000006</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="E152" s="8">
-        <v>69</v>
-      </c>
-      <c r="F152" s="7">
-        <v>86</v>
-      </c>
-      <c r="G152" s="7">
-        <v>88</v>
+        <v>1651</v>
+      </c>
+      <c r="E152" s="6">
+        <v>76</v>
+      </c>
+      <c r="F152" s="6">
+        <v>77</v>
+      </c>
+      <c r="G152" s="8">
+        <v>68</v>
       </c>
       <c r="H152" s="2" t="s">
-        <v>31</v>
+        <v>1653</v>
       </c>
       <c r="I152" s="2" t="s">
-        <v>273</v>
+        <v>1662</v>
       </c>
       <c r="J152" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K152" s="2" t="s">
-        <v>274</v>
+        <v>1669</v>
       </c>
       <c r="L152" s="2">
         <f>(SUM(7*E152,G152,2*F152))/10</f>
-        <v>74.3</v>
+        <v>75.400000000000006</v>
       </c>
     </row>
     <row r="153" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -11574,29 +11577,32 @@
         <v>74.3</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="E153" s="6">
-        <v>74</v>
+        <v>272</v>
+      </c>
+      <c r="E153" s="8">
+        <v>69</v>
       </c>
       <c r="F153" s="7">
-        <v>84</v>
-      </c>
-      <c r="G153" s="8">
-        <v>67</v>
+        <v>86</v>
+      </c>
+      <c r="G153" s="7">
+        <v>88</v>
       </c>
       <c r="H153" s="2" t="s">
-        <v>135</v>
+        <v>31</v>
       </c>
       <c r="I153" s="2" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="J153" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="K153" s="2" t="s">
+        <v>274</v>
+      </c>
       <c r="L153" s="2">
         <f>(SUM(7*E153,G153,2*F153))/10</f>
-        <v>75.3</v>
+        <v>74.3</v>
       </c>
     </row>
     <row r="154" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -11607,22 +11613,22 @@
         <v>74.3</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E154" s="6">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F154" s="7">
-        <v>85</v>
-      </c>
-      <c r="G154" s="6">
-        <v>79</v>
+        <v>84</v>
+      </c>
+      <c r="G154" s="8">
+        <v>67</v>
       </c>
       <c r="H154" s="2" t="s">
-        <v>12</v>
+        <v>135</v>
       </c>
       <c r="I154" s="2" t="s">
-        <v>183</v>
+        <v>276</v>
       </c>
       <c r="J154" s="3" t="s">
         <v>14</v>
@@ -11633,39 +11639,36 @@
       </c>
     </row>
     <row r="155" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A155" s="2">
-        <v>2026</v>
-      </c>
       <c r="B155" s="2">
         <v>154</v>
       </c>
       <c r="C155" s="6">
         <v>74.3</v>
       </c>
-      <c r="D155" s="12" t="s">
-        <v>1315</v>
+      <c r="D155" s="2" t="s">
+        <v>277</v>
       </c>
       <c r="E155" s="6">
-        <v>75</v>
-      </c>
-      <c r="F155" s="8">
-        <v>60</v>
-      </c>
-      <c r="G155" s="2">
-        <v>48</v>
-      </c>
-      <c r="H155" s="12" t="s">
-        <v>1264</v>
-      </c>
-      <c r="I155" s="12" t="s">
-        <v>1297</v>
-      </c>
-      <c r="J155" s="13" t="s">
-        <v>1269</v>
+        <v>72</v>
+      </c>
+      <c r="F155" s="7">
+        <v>85</v>
+      </c>
+      <c r="G155" s="6">
+        <v>79</v>
+      </c>
+      <c r="H155" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I155" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="J155" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="L155" s="2">
         <f>(SUM(7*E155,G155,2*F155))/10</f>
-        <v>69.3</v>
+        <v>75.3</v>
       </c>
     </row>
     <row r="156" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -11676,35 +11679,32 @@
         <v>155</v>
       </c>
       <c r="C156" s="6">
-        <v>74.2</v>
-      </c>
-      <c r="D156" s="2" t="s">
-        <v>1646</v>
+        <v>74.3</v>
+      </c>
+      <c r="D156" s="12" t="s">
+        <v>1315</v>
       </c>
       <c r="E156" s="6">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F156" s="8">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="G156" s="2">
-        <v>57</v>
-      </c>
-      <c r="H156" s="2" t="s">
-        <v>1655</v>
-      </c>
-      <c r="I156" s="2" t="s">
-        <v>1658</v>
-      </c>
-      <c r="J156" s="3" t="s">
-        <v>1667</v>
-      </c>
-      <c r="K156" s="2" t="s">
-        <v>1673</v>
+        <v>48</v>
+      </c>
+      <c r="H156" s="12" t="s">
+        <v>1264</v>
+      </c>
+      <c r="I156" s="12" t="s">
+        <v>1297</v>
+      </c>
+      <c r="J156" s="13" t="s">
+        <v>1269</v>
       </c>
       <c r="L156" s="2">
         <f>(SUM(7*E156,G156,2*F156))/10</f>
-        <v>72.2</v>
+        <v>69.3</v>
       </c>
     </row>
     <row r="157" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -11715,32 +11715,35 @@
         <v>156</v>
       </c>
       <c r="C157" s="6">
-        <v>74.099999999999994</v>
-      </c>
-      <c r="D157" s="12" t="s">
-        <v>1313</v>
+        <v>74.2</v>
+      </c>
+      <c r="D157" s="2" t="s">
+        <v>1646</v>
       </c>
       <c r="E157" s="6">
-        <v>74</v>
-      </c>
-      <c r="F157" s="6">
-        <v>70</v>
+        <v>77</v>
+      </c>
+      <c r="F157" s="8">
+        <v>63</v>
       </c>
       <c r="G157" s="2">
-        <v>53</v>
-      </c>
-      <c r="H157" s="12" t="s">
-        <v>1264</v>
-      </c>
-      <c r="I157" s="12" t="s">
-        <v>1285</v>
-      </c>
-      <c r="J157" s="13" t="s">
-        <v>1272</v>
+        <v>57</v>
+      </c>
+      <c r="H157" s="2" t="s">
+        <v>1655</v>
+      </c>
+      <c r="I157" s="2" t="s">
+        <v>1658</v>
+      </c>
+      <c r="J157" s="3" t="s">
+        <v>1667</v>
+      </c>
+      <c r="K157" s="2" t="s">
+        <v>1673</v>
       </c>
       <c r="L157" s="2">
         <f>(SUM(7*E157,G157,2*F157))/10</f>
-        <v>71.099999999999994</v>
+        <v>72.2</v>
       </c>
     </row>
     <row r="158" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -11753,72 +11756,69 @@
       <c r="C158" s="6">
         <v>74.099999999999994</v>
       </c>
-      <c r="D158" s="2" t="s">
-        <v>1525</v>
+      <c r="D158" s="12" t="s">
+        <v>1313</v>
       </c>
       <c r="E158" s="6">
-        <v>75</v>
-      </c>
-      <c r="F158" s="8">
-        <v>67</v>
-      </c>
-      <c r="G158" s="6">
-        <v>72</v>
-      </c>
-      <c r="H158" s="2" t="s">
-        <v>1496</v>
-      </c>
-      <c r="I158" s="2" t="s">
-        <v>1530</v>
-      </c>
-      <c r="J158" s="3" t="s">
-        <v>1550</v>
+        <v>74</v>
+      </c>
+      <c r="F158" s="6">
+        <v>70</v>
+      </c>
+      <c r="G158" s="2">
+        <v>53</v>
+      </c>
+      <c r="H158" s="12" t="s">
+        <v>1264</v>
+      </c>
+      <c r="I158" s="12" t="s">
+        <v>1285</v>
+      </c>
+      <c r="J158" s="13" t="s">
+        <v>1272</v>
       </c>
       <c r="L158" s="2">
         <f>(SUM(7*E158,G158,2*F158))/10</f>
-        <v>73.099999999999994</v>
+        <v>71.099999999999994</v>
       </c>
     </row>
     <row r="159" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A159" s="2">
+        <v>2026</v>
+      </c>
       <c r="B159" s="2">
         <v>158</v>
       </c>
       <c r="C159" s="6">
-        <v>74</v>
+        <v>74.099999999999994</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>278</v>
+        <v>1525</v>
       </c>
       <c r="E159" s="6">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="F159" s="8">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G159" s="6">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H159" s="2" t="s">
-        <v>279</v>
+        <v>1496</v>
       </c>
       <c r="I159" s="2" t="s">
-        <v>280</v>
+        <v>1530</v>
       </c>
       <c r="J159" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="K159" s="2" t="s">
-        <v>281</v>
+        <v>1550</v>
       </c>
       <c r="L159" s="2">
         <f>(SUM(7*E159,G159,2*F159))/10</f>
-        <v>70</v>
+        <v>73.099999999999994</v>
       </c>
     </row>
     <row r="160" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A160" s="2">
-        <v>2026</v>
-      </c>
       <c r="B160" s="2">
         <v>159</v>
       </c>
@@ -11826,68 +11826,71 @@
         <v>74</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>1409</v>
+        <v>278</v>
       </c>
       <c r="E160" s="6">
-        <v>75</v>
-      </c>
-      <c r="F160" s="2">
-        <v>59</v>
-      </c>
-      <c r="G160" s="2">
-        <v>47</v>
+        <v>71</v>
+      </c>
+      <c r="F160" s="8">
+        <v>66</v>
+      </c>
+      <c r="G160" s="6">
+        <v>71</v>
       </c>
       <c r="H160" s="2" t="s">
-        <v>1418</v>
+        <v>279</v>
       </c>
       <c r="I160" s="2" t="s">
-        <v>36</v>
+        <v>280</v>
       </c>
       <c r="J160" s="3" t="s">
-        <v>1438</v>
+        <v>18</v>
+      </c>
+      <c r="K160" s="2" t="s">
+        <v>281</v>
       </c>
       <c r="L160" s="2">
         <f>(SUM(7*E160,G160,2*F160))/10</f>
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="161" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A161" s="2">
+        <v>2026</v>
+      </c>
       <c r="B161" s="2">
         <v>160</v>
       </c>
       <c r="C161" s="6">
-        <v>73.900000000000006</v>
+        <v>74</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>282</v>
+        <v>1409</v>
       </c>
       <c r="E161" s="6">
-        <v>70</v>
-      </c>
-      <c r="F161" s="6">
         <v>75</v>
       </c>
-      <c r="G161" s="6">
-        <v>74</v>
+      <c r="F161" s="2">
+        <v>59</v>
+      </c>
+      <c r="G161" s="2">
+        <v>47</v>
       </c>
       <c r="H161" s="2" t="s">
-        <v>104</v>
+        <v>1418</v>
       </c>
       <c r="I161" s="2" t="s">
-        <v>106</v>
+        <v>36</v>
       </c>
       <c r="J161" s="3" t="s">
-        <v>18</v>
+        <v>1438</v>
       </c>
       <c r="L161" s="2">
         <f>(SUM(7*E161,G161,2*F161))/10</f>
-        <v>71.400000000000006</v>
+        <v>69</v>
       </c>
     </row>
     <row r="162" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A162" s="2">
-        <v>2026</v>
-      </c>
       <c r="B162" s="2">
         <v>161</v>
       </c>
@@ -11895,62 +11898,65 @@
         <v>73.900000000000006</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>1650</v>
+        <v>282</v>
       </c>
       <c r="E162" s="6">
+        <v>70</v>
+      </c>
+      <c r="F162" s="6">
         <v>75</v>
       </c>
-      <c r="F162" s="6">
-        <v>70</v>
-      </c>
-      <c r="G162" s="8">
-        <v>64</v>
+      <c r="G162" s="6">
+        <v>74</v>
       </c>
       <c r="H162" s="2" t="s">
-        <v>1653</v>
+        <v>104</v>
       </c>
       <c r="I162" s="2" t="s">
-        <v>1661</v>
+        <v>106</v>
       </c>
       <c r="J162" s="3" t="s">
-        <v>1667</v>
+        <v>18</v>
       </c>
       <c r="L162" s="2">
         <f>(SUM(7*E162,G162,2*F162))/10</f>
-        <v>72.900000000000006</v>
+        <v>71.400000000000006</v>
       </c>
     </row>
     <row r="163" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A163" s="2">
+        <v>2026</v>
+      </c>
       <c r="B163" s="2">
         <v>162</v>
       </c>
       <c r="C163" s="6">
-        <v>73.8</v>
+        <v>73.900000000000006</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>283</v>
+        <v>1650</v>
       </c>
       <c r="E163" s="6">
-        <v>72</v>
-      </c>
-      <c r="F163" s="8">
-        <v>63</v>
-      </c>
-      <c r="G163" s="2">
-        <v>53</v>
+        <v>75</v>
+      </c>
+      <c r="F163" s="6">
+        <v>70</v>
+      </c>
+      <c r="G163" s="8">
+        <v>64</v>
       </c>
       <c r="H163" s="2" t="s">
-        <v>114</v>
+        <v>1653</v>
       </c>
       <c r="I163" s="2" t="s">
-        <v>36</v>
+        <v>1661</v>
       </c>
       <c r="J163" s="3" t="s">
-        <v>37</v>
+        <v>1667</v>
       </c>
       <c r="L163" s="2">
         <f>(SUM(7*E163,G163,2*F163))/10</f>
-        <v>68.3</v>
+        <v>72.900000000000006</v>
       </c>
     </row>
     <row r="164" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -11961,38 +11967,32 @@
         <v>73.8</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="E164" s="7">
-        <v>82</v>
+        <v>283</v>
+      </c>
+      <c r="E164" s="6">
+        <v>72</v>
       </c>
       <c r="F164" s="8">
-        <v>64</v>
-      </c>
-      <c r="G164" s="6">
-        <v>76</v>
+        <v>63</v>
+      </c>
+      <c r="G164" s="2">
+        <v>53</v>
       </c>
       <c r="H164" s="2" t="s">
-        <v>61</v>
+        <v>114</v>
       </c>
       <c r="I164" s="2" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="J164" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="K164" s="2" t="s">
-        <v>285</v>
+        <v>37</v>
       </c>
       <c r="L164" s="2">
         <f>(SUM(7*E164,G164,2*F164))/10</f>
-        <v>77.8</v>
+        <v>68.3</v>
       </c>
     </row>
     <row r="165" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A165" s="2">
-        <v>2026</v>
-      </c>
       <c r="B165" s="2">
         <v>164</v>
       </c>
@@ -12000,29 +12000,32 @@
         <v>73.8</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>1411</v>
-      </c>
-      <c r="E165" s="6">
-        <v>73</v>
+        <v>284</v>
+      </c>
+      <c r="E165" s="7">
+        <v>82</v>
       </c>
       <c r="F165" s="8">
-        <v>65</v>
-      </c>
-      <c r="G165" s="8">
-        <v>67</v>
+        <v>64</v>
+      </c>
+      <c r="G165" s="6">
+        <v>76</v>
       </c>
       <c r="H165" s="2" t="s">
-        <v>1418</v>
+        <v>61</v>
       </c>
       <c r="I165" s="2" t="s">
-        <v>1432</v>
+        <v>17</v>
       </c>
       <c r="J165" s="3" t="s">
-        <v>1440</v>
+        <v>42</v>
+      </c>
+      <c r="K165" s="2" t="s">
+        <v>285</v>
       </c>
       <c r="L165" s="2">
         <f>(SUM(7*E165,G165,2*F165))/10</f>
-        <v>70.8</v>
+        <v>77.8</v>
       </c>
     </row>
     <row r="166" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -12036,62 +12039,65 @@
         <v>73.8</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>1696</v>
+        <v>1411</v>
       </c>
       <c r="E166" s="6">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F166" s="8">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G166" s="8">
         <v>67</v>
       </c>
       <c r="H166" s="2" t="s">
-        <v>1702</v>
+        <v>1418</v>
       </c>
       <c r="I166" s="2" t="s">
-        <v>1704</v>
+        <v>1432</v>
       </c>
       <c r="J166" s="3" t="s">
-        <v>1710</v>
+        <v>1440</v>
       </c>
       <c r="L166" s="2">
         <f>(SUM(7*E166,G166,2*F166))/10</f>
-        <v>71.3</v>
+        <v>70.8</v>
       </c>
     </row>
     <row r="167" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A167" s="2">
+        <v>2026</v>
+      </c>
       <c r="B167" s="2">
         <v>166</v>
       </c>
       <c r="C167" s="6">
-        <v>73.7</v>
+        <v>73.8</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>286</v>
+        <v>1696</v>
       </c>
       <c r="E167" s="6">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F167" s="8">
-        <v>60</v>
-      </c>
-      <c r="G167" s="2">
-        <v>57</v>
+        <v>64</v>
+      </c>
+      <c r="G167" s="8">
+        <v>67</v>
       </c>
       <c r="H167" s="2" t="s">
-        <v>58</v>
+        <v>1702</v>
       </c>
       <c r="I167" s="2" t="s">
-        <v>49</v>
+        <v>1704</v>
       </c>
       <c r="J167" s="3" t="s">
-        <v>23</v>
+        <v>1710</v>
       </c>
       <c r="L167" s="2">
         <f>(SUM(7*E167,G167,2*F167))/10</f>
-        <v>70.2</v>
+        <v>71.3</v>
       </c>
     </row>
     <row r="168" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -12102,32 +12108,29 @@
         <v>73.7</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E168" s="6">
-        <v>70</v>
-      </c>
-      <c r="F168" s="6">
-        <v>79</v>
-      </c>
-      <c r="G168" s="6">
-        <v>79</v>
+        <v>75</v>
+      </c>
+      <c r="F168" s="8">
+        <v>60</v>
+      </c>
+      <c r="G168" s="2">
+        <v>57</v>
       </c>
       <c r="H168" s="2" t="s">
-        <v>288</v>
+        <v>58</v>
       </c>
       <c r="I168" s="2" t="s">
-        <v>228</v>
+        <v>49</v>
       </c>
       <c r="J168" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="K168" s="2" t="s">
-        <v>289</v>
+        <v>23</v>
       </c>
       <c r="L168" s="2">
         <f>(SUM(7*E168,G168,2*F168))/10</f>
-        <v>72.7</v>
+        <v>70.2</v>
       </c>
     </row>
     <row r="169" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -12135,35 +12138,35 @@
         <v>168</v>
       </c>
       <c r="C169" s="6">
-        <v>73.599999999999994</v>
+        <v>73.7</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>212</v>
+        <v>287</v>
       </c>
       <c r="E169" s="6">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F169" s="6">
-        <v>70</v>
-      </c>
-      <c r="G169" s="2">
-        <v>57</v>
+        <v>79</v>
+      </c>
+      <c r="G169" s="6">
+        <v>79</v>
       </c>
       <c r="H169" s="2" t="s">
-        <v>213</v>
+        <v>288</v>
       </c>
       <c r="I169" s="2" t="s">
-        <v>17</v>
+        <v>228</v>
       </c>
       <c r="J169" s="3" t="s">
-        <v>122</v>
+        <v>88</v>
       </c>
       <c r="K169" s="2" t="s">
-        <v>115</v>
+        <v>289</v>
       </c>
       <c r="L169" s="2">
         <f>(SUM(7*E169,G169,2*F169))/10</f>
-        <v>70.099999999999994</v>
+        <v>72.7</v>
       </c>
     </row>
     <row r="170" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -12174,35 +12177,35 @@
         <v>73.599999999999994</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>290</v>
+        <v>212</v>
       </c>
       <c r="E170" s="6">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F170" s="6">
-        <v>74</v>
-      </c>
-      <c r="G170" s="7">
-        <v>81</v>
+        <v>70</v>
+      </c>
+      <c r="G170" s="2">
+        <v>57</v>
       </c>
       <c r="H170" s="2" t="s">
-        <v>291</v>
+        <v>213</v>
       </c>
       <c r="I170" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="J170" s="3" t="s">
-        <v>140</v>
+        <v>122</v>
+      </c>
+      <c r="K170" s="2" t="s">
+        <v>115</v>
       </c>
       <c r="L170" s="2">
         <f>(SUM(7*E170,G170,2*F170))/10</f>
-        <v>72.599999999999994</v>
+        <v>70.099999999999994</v>
       </c>
     </row>
     <row r="171" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A171" s="2">
-        <v>2026</v>
-      </c>
       <c r="B171" s="2">
         <v>170</v>
       </c>
@@ -12210,32 +12213,29 @@
         <v>73.599999999999994</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>1505</v>
+        <v>290</v>
       </c>
       <c r="E171" s="6">
-        <v>77</v>
-      </c>
-      <c r="F171" s="2">
-        <v>51</v>
-      </c>
-      <c r="G171" s="2">
-        <v>50</v>
+        <v>71</v>
+      </c>
+      <c r="F171" s="6">
+        <v>74</v>
+      </c>
+      <c r="G171" s="7">
+        <v>81</v>
       </c>
       <c r="H171" s="2" t="s">
-        <v>1527</v>
+        <v>291</v>
       </c>
       <c r="I171" s="2" t="s">
-        <v>1534</v>
+        <v>13</v>
       </c>
       <c r="J171" s="3" t="s">
-        <v>1544</v>
-      </c>
-      <c r="K171" s="2" t="s">
-        <v>1539</v>
+        <v>140</v>
       </c>
       <c r="L171" s="2">
         <f>(SUM(7*E171,G171,2*F171))/10</f>
-        <v>69.099999999999994</v>
+        <v>72.599999999999994</v>
       </c>
     </row>
     <row r="172" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -12249,32 +12249,32 @@
         <v>73.599999999999994</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>1641</v>
+        <v>1505</v>
       </c>
       <c r="E172" s="6">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F172" s="2">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="G172" s="2">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="H172" s="2" t="s">
-        <v>1653</v>
+        <v>1527</v>
       </c>
       <c r="I172" s="2" t="s">
-        <v>36</v>
+        <v>1534</v>
       </c>
       <c r="J172" s="3" t="s">
-        <v>1664</v>
+        <v>1544</v>
       </c>
       <c r="K172" s="2" t="s">
-        <v>1671</v>
+        <v>1539</v>
       </c>
       <c r="L172" s="2">
         <f>(SUM(7*E172,G172,2*F172))/10</f>
-        <v>67.599999999999994</v>
+        <v>69.099999999999994</v>
       </c>
     </row>
     <row r="173" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -12285,35 +12285,41 @@
         <v>172</v>
       </c>
       <c r="C173" s="6">
-        <v>73.5</v>
+        <v>73.599999999999994</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>1428</v>
+        <v>1641</v>
       </c>
       <c r="E173" s="6">
         <v>74</v>
       </c>
-      <c r="F173" s="8">
-        <v>62</v>
-      </c>
-      <c r="G173" s="8">
-        <v>68</v>
+      <c r="F173" s="2">
+        <v>56</v>
+      </c>
+      <c r="G173" s="2">
+        <v>46</v>
       </c>
       <c r="H173" s="2" t="s">
-        <v>1430</v>
+        <v>1653</v>
       </c>
       <c r="I173" s="2" t="s">
-        <v>1432</v>
+        <v>36</v>
       </c>
       <c r="J173" s="3" t="s">
-        <v>1443</v>
+        <v>1664</v>
+      </c>
+      <c r="K173" s="2" t="s">
+        <v>1671</v>
       </c>
       <c r="L173" s="2">
         <f>(SUM(7*E173,G173,2*F173))/10</f>
-        <v>71</v>
+        <v>67.599999999999994</v>
       </c>
     </row>
     <row r="174" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A174" s="2">
+        <v>2026</v>
+      </c>
       <c r="B174" s="2">
         <v>173</v>
       </c>
@@ -12321,32 +12327,29 @@
         <v>73.5</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>292</v>
+        <v>1428</v>
       </c>
       <c r="E174" s="6">
-        <v>77</v>
-      </c>
-      <c r="F174" s="2">
-        <v>53</v>
-      </c>
-      <c r="G174" s="2">
-        <v>45</v>
+        <v>74</v>
+      </c>
+      <c r="F174" s="8">
+        <v>62</v>
+      </c>
+      <c r="G174" s="8">
+        <v>68</v>
       </c>
       <c r="H174" s="2" t="s">
-        <v>224</v>
+        <v>1430</v>
       </c>
       <c r="I174" s="2" t="s">
-        <v>72</v>
+        <v>1432</v>
       </c>
       <c r="J174" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="K174" s="2" t="s">
-        <v>293</v>
+        <v>1443</v>
       </c>
       <c r="L174" s="2">
         <f>(SUM(7*E174,G174,2*F174))/10</f>
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="175" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -12357,25 +12360,28 @@
         <v>73.5</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="E175" s="6">
-        <v>71</v>
-      </c>
-      <c r="F175" s="8">
-        <v>64</v>
-      </c>
-      <c r="G175" s="8">
-        <v>65</v>
+        <v>77</v>
+      </c>
+      <c r="F175" s="2">
+        <v>53</v>
+      </c>
+      <c r="G175" s="2">
+        <v>45</v>
       </c>
       <c r="H175" s="2" t="s">
-        <v>31</v>
+        <v>224</v>
       </c>
       <c r="I175" s="2" t="s">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="J175" s="3" t="s">
-        <v>132</v>
+        <v>23</v>
+      </c>
+      <c r="K175" s="2" t="s">
+        <v>293</v>
       </c>
       <c r="L175" s="2">
         <f>(SUM(7*E175,G175,2*F175))/10</f>
@@ -12390,35 +12396,32 @@
         <v>73.5</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E176" s="6">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F176" s="8">
+        <v>64</v>
+      </c>
+      <c r="G176" s="8">
         <v>65</v>
       </c>
-      <c r="G176" s="8">
-        <v>66</v>
-      </c>
       <c r="H176" s="2" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="I176" s="2" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="J176" s="3" t="s">
-        <v>23</v>
+        <v>132</v>
       </c>
       <c r="L176" s="2">
         <f>(SUM(7*E176,G176,2*F176))/10</f>
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="177" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A177" s="2">
-        <v>2026</v>
-      </c>
       <c r="B177" s="2">
         <v>176</v>
       </c>
@@ -12426,25 +12429,25 @@
         <v>73.5</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>1568</v>
+        <v>295</v>
       </c>
       <c r="E177" s="6">
         <v>72</v>
       </c>
       <c r="F177" s="8">
-        <v>69</v>
-      </c>
-      <c r="G177" s="2">
-        <v>58</v>
+        <v>65</v>
+      </c>
+      <c r="G177" s="8">
+        <v>66</v>
       </c>
       <c r="H177" s="2" t="s">
         <v>48</v>
       </c>
       <c r="I177" s="2" t="s">
-        <v>1577</v>
+        <v>41</v>
       </c>
       <c r="J177" s="3" t="s">
-        <v>1582</v>
+        <v>23</v>
       </c>
       <c r="L177" s="2">
         <f>(SUM(7*E177,G177,2*F177))/10</f>
@@ -12459,38 +12462,38 @@
         <v>177</v>
       </c>
       <c r="C178" s="6">
-        <v>73.400000000000006</v>
+        <v>73.5</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>1386</v>
-      </c>
-      <c r="E178" s="7">
-        <v>80</v>
-      </c>
-      <c r="F178" s="2">
-        <v>47</v>
+        <v>1568</v>
+      </c>
+      <c r="E178" s="6">
+        <v>72</v>
+      </c>
+      <c r="F178" s="8">
+        <v>69</v>
       </c>
       <c r="G178" s="2">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="H178" s="2" t="s">
-        <v>1391</v>
+        <v>48</v>
       </c>
       <c r="I178" s="2" t="s">
-        <v>1398</v>
+        <v>1577</v>
       </c>
       <c r="J178" s="3" t="s">
-        <v>1399</v>
-      </c>
-      <c r="K178" s="2" t="s">
-        <v>1389</v>
+        <v>1582</v>
       </c>
       <c r="L178" s="2">
         <f>(SUM(7*E178,G178,2*F178))/10</f>
-        <v>69.400000000000006</v>
+        <v>70</v>
       </c>
     </row>
     <row r="179" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A179" s="2">
+        <v>2026</v>
+      </c>
       <c r="B179" s="2">
         <v>178</v>
       </c>
@@ -12498,32 +12501,32 @@
         <v>73.400000000000006</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="E179" s="6">
-        <v>75</v>
-      </c>
-      <c r="F179" s="7">
-        <v>83</v>
-      </c>
-      <c r="G179" s="5">
-        <v>93</v>
+        <v>1386</v>
+      </c>
+      <c r="E179" s="7">
+        <v>80</v>
+      </c>
+      <c r="F179" s="2">
+        <v>47</v>
+      </c>
+      <c r="G179" s="2">
+        <v>40</v>
       </c>
       <c r="H179" s="2" t="s">
-        <v>297</v>
+        <v>1391</v>
       </c>
       <c r="I179" s="2" t="s">
-        <v>298</v>
+        <v>1398</v>
       </c>
       <c r="J179" s="3" t="s">
-        <v>42</v>
+        <v>1399</v>
       </c>
       <c r="K179" s="2" t="s">
-        <v>299</v>
+        <v>1389</v>
       </c>
       <c r="L179" s="2">
         <f>(SUM(7*E179,G179,2*F179))/10</f>
-        <v>78.400000000000006</v>
+        <v>69.400000000000006</v>
       </c>
     </row>
     <row r="180" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -12534,29 +12537,32 @@
         <v>73.400000000000006</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="E180" s="6">
-        <v>74</v>
-      </c>
-      <c r="F180" s="8">
-        <v>67</v>
-      </c>
-      <c r="G180" s="6">
-        <v>72</v>
+        <v>75</v>
+      </c>
+      <c r="F180" s="7">
+        <v>83</v>
+      </c>
+      <c r="G180" s="5">
+        <v>93</v>
       </c>
       <c r="H180" s="2" t="s">
-        <v>64</v>
+        <v>297</v>
       </c>
       <c r="I180" s="2" t="s">
-        <v>41</v>
+        <v>298</v>
       </c>
       <c r="J180" s="3" t="s">
-        <v>140</v>
+        <v>42</v>
+      </c>
+      <c r="K180" s="2" t="s">
+        <v>299</v>
       </c>
       <c r="L180" s="2">
         <f>(SUM(7*E180,G180,2*F180))/10</f>
-        <v>72.400000000000006</v>
+        <v>78.400000000000006</v>
       </c>
     </row>
     <row r="181" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -12567,29 +12573,29 @@
         <v>73.400000000000006</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E181" s="6">
         <v>74</v>
       </c>
-      <c r="F181" s="7">
-        <v>88</v>
-      </c>
-      <c r="G181" s="5">
-        <v>90</v>
+      <c r="F181" s="8">
+        <v>67</v>
+      </c>
+      <c r="G181" s="6">
+        <v>72</v>
       </c>
       <c r="H181" s="2" t="s">
-        <v>302</v>
+        <v>64</v>
       </c>
       <c r="I181" s="2" t="s">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="J181" s="3" t="s">
-        <v>42</v>
+        <v>140</v>
       </c>
       <c r="L181" s="2">
         <f>(SUM(7*E181,G181,2*F181))/10</f>
-        <v>78.400000000000006</v>
+        <v>72.400000000000006</v>
       </c>
     </row>
     <row r="182" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -12600,101 +12606,101 @@
         <v>73.400000000000006</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="E182" s="6">
-        <v>72</v>
-      </c>
-      <c r="F182" s="8">
-        <v>65</v>
-      </c>
-      <c r="G182" s="6">
-        <v>75</v>
+        <v>74</v>
+      </c>
+      <c r="F182" s="7">
+        <v>88</v>
+      </c>
+      <c r="G182" s="5">
+        <v>90</v>
       </c>
       <c r="H182" s="2" t="s">
-        <v>135</v>
+        <v>302</v>
       </c>
       <c r="I182" s="2" t="s">
-        <v>276</v>
+        <v>79</v>
       </c>
       <c r="J182" s="3" t="s">
-        <v>122</v>
+        <v>42</v>
       </c>
       <c r="L182" s="2">
         <f>(SUM(7*E182,G182,2*F182))/10</f>
-        <v>70.900000000000006</v>
+        <v>78.400000000000006</v>
       </c>
     </row>
     <row r="183" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A183" s="2">
-        <v>2026</v>
-      </c>
       <c r="B183" s="2">
         <v>182</v>
       </c>
       <c r="C183" s="6">
         <v>73.400000000000006</v>
       </c>
-      <c r="D183" s="12" t="s">
-        <v>1353</v>
+      <c r="D183" s="2" t="s">
+        <v>303</v>
       </c>
       <c r="E183" s="6">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F183" s="8">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G183" s="6">
-        <v>71</v>
-      </c>
-      <c r="H183" s="12" t="s">
-        <v>1264</v>
-      </c>
-      <c r="I183" s="12" t="s">
-        <v>1362</v>
-      </c>
-      <c r="J183" s="13" t="s">
-        <v>1310</v>
-      </c>
-      <c r="K183" s="12" t="s">
-        <v>1359</v>
+        <v>75</v>
+      </c>
+      <c r="H183" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="I183" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="J183" s="3" t="s">
+        <v>122</v>
       </c>
       <c r="L183" s="2">
         <f>(SUM(7*E183,G183,2*F183))/10</f>
-        <v>71.400000000000006</v>
+        <v>70.900000000000006</v>
       </c>
     </row>
     <row r="184" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A184" s="2">
+        <v>2026</v>
+      </c>
       <c r="B184" s="2">
         <v>183</v>
       </c>
       <c r="C184" s="6">
-        <v>73.3</v>
-      </c>
-      <c r="D184" s="2" t="s">
-        <v>304</v>
+        <v>73.400000000000006</v>
+      </c>
+      <c r="D184" s="12" t="s">
+        <v>1353</v>
       </c>
       <c r="E184" s="6">
+        <v>73</v>
+      </c>
+      <c r="F184" s="8">
+        <v>66</v>
+      </c>
+      <c r="G184" s="6">
         <v>71</v>
       </c>
-      <c r="F184" s="7">
-        <v>85</v>
-      </c>
-      <c r="G184" s="7">
-        <v>88</v>
-      </c>
-      <c r="H184" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="I184" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="J184" s="3" t="s">
-        <v>65</v>
+      <c r="H184" s="12" t="s">
+        <v>1264</v>
+      </c>
+      <c r="I184" s="12" t="s">
+        <v>1362</v>
+      </c>
+      <c r="J184" s="13" t="s">
+        <v>1310</v>
+      </c>
+      <c r="K184" s="12" t="s">
+        <v>1359</v>
       </c>
       <c r="L184" s="2">
         <f>(SUM(7*E184,G184,2*F184))/10</f>
-        <v>75.5</v>
+        <v>71.400000000000006</v>
       </c>
     </row>
     <row r="185" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -12702,35 +12708,32 @@
         <v>184</v>
       </c>
       <c r="C185" s="6">
-        <v>73.2</v>
+        <v>73.3</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="E185" s="7">
-        <v>86</v>
-      </c>
-      <c r="F185" s="2">
-        <v>20</v>
-      </c>
-      <c r="G185" s="2">
-        <v>25</v>
+        <v>304</v>
+      </c>
+      <c r="E185" s="6">
+        <v>71</v>
+      </c>
+      <c r="F185" s="7">
+        <v>85</v>
+      </c>
+      <c r="G185" s="7">
+        <v>88</v>
       </c>
       <c r="H185" s="2" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="I185" s="2" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="J185" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="K185" s="2" t="s">
-        <v>306</v>
+        <v>65</v>
       </c>
       <c r="L185" s="2">
         <f>(SUM(7*E185,G185,2*F185))/10</f>
-        <v>66.7</v>
+        <v>75.5</v>
       </c>
     </row>
     <row r="186" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -12741,29 +12744,32 @@
         <v>73.2</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="E186" s="6">
-        <v>74</v>
+        <v>305</v>
+      </c>
+      <c r="E186" s="7">
+        <v>86</v>
       </c>
       <c r="F186" s="2">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="G186" s="2">
-        <v>54</v>
+        <v>25</v>
       </c>
       <c r="H186" s="2" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="I186" s="2" t="s">
         <v>36</v>
       </c>
       <c r="J186" s="3" t="s">
-        <v>37</v>
+        <v>146</v>
+      </c>
+      <c r="K186" s="2" t="s">
+        <v>306</v>
       </c>
       <c r="L186" s="2">
         <f>(SUM(7*E186,G186,2*F186))/10</f>
-        <v>68.2</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="187" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -12774,29 +12780,29 @@
         <v>73.2</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E187" s="6">
-        <v>71</v>
-      </c>
-      <c r="F187" s="6">
-        <v>70</v>
-      </c>
-      <c r="G187" s="8">
-        <v>65</v>
+        <v>74</v>
+      </c>
+      <c r="F187" s="2">
+        <v>55</v>
+      </c>
+      <c r="G187" s="2">
+        <v>54</v>
       </c>
       <c r="H187" s="2" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="I187" s="2" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="J187" s="3" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="L187" s="2">
         <f>(SUM(7*E187,G187,2*F187))/10</f>
-        <v>70.2</v>
+        <v>68.2</v>
       </c>
     </row>
     <row r="188" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -12804,32 +12810,32 @@
         <v>187</v>
       </c>
       <c r="C188" s="6">
-        <v>73.099999999999994</v>
+        <v>73.2</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E188" s="6">
         <v>71</v>
       </c>
-      <c r="F188" s="8">
-        <v>66</v>
+      <c r="F188" s="6">
+        <v>70</v>
       </c>
       <c r="G188" s="8">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="H188" s="2" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="I188" s="2" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="J188" s="3" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="L188" s="2">
         <f>(SUM(7*E188,G188,2*F188))/10</f>
-        <v>69.599999999999994</v>
+        <v>70.2</v>
       </c>
     </row>
     <row r="189" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -12840,104 +12846,101 @@
         <v>73.099999999999994</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="E189" s="8">
+        <v>309</v>
+      </c>
+      <c r="E189" s="6">
+        <v>71</v>
+      </c>
+      <c r="F189" s="8">
         <v>66</v>
       </c>
-      <c r="F189" s="7">
-        <v>82</v>
-      </c>
       <c r="G189" s="8">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H189" s="2" t="s">
-        <v>297</v>
+        <v>31</v>
       </c>
       <c r="I189" s="2" t="s">
-        <v>218</v>
+        <v>36</v>
       </c>
       <c r="J189" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="K189" s="2" t="s">
-        <v>311</v>
+        <v>32</v>
       </c>
       <c r="L189" s="2">
         <f>(SUM(7*E189,G189,2*F189))/10</f>
-        <v>69.099999999999994</v>
+        <v>69.599999999999994</v>
       </c>
     </row>
     <row r="190" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A190" s="2">
-        <v>2026</v>
-      </c>
       <c r="B190" s="2">
         <v>189</v>
       </c>
       <c r="C190" s="6">
         <v>73.099999999999994</v>
       </c>
-      <c r="D190" s="12" t="s">
-        <v>1259</v>
-      </c>
-      <c r="E190" s="6">
-        <v>75</v>
-      </c>
-      <c r="F190" s="8">
-        <v>60</v>
-      </c>
-      <c r="G190" s="2">
-        <v>56</v>
-      </c>
-      <c r="H190" s="12" t="s">
-        <v>1264</v>
-      </c>
-      <c r="I190" s="12" t="s">
-        <v>1266</v>
-      </c>
-      <c r="J190" s="13" t="s">
-        <v>1272</v>
+      <c r="D190" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="E190" s="8">
+        <v>66</v>
+      </c>
+      <c r="F190" s="7">
+        <v>82</v>
+      </c>
+      <c r="G190" s="8">
+        <v>65</v>
+      </c>
+      <c r="H190" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="I190" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="J190" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K190" s="2" t="s">
+        <v>311</v>
       </c>
       <c r="L190" s="2">
         <f>(SUM(7*E190,G190,2*F190))/10</f>
-        <v>70.099999999999994</v>
+        <v>69.099999999999994</v>
       </c>
     </row>
     <row r="191" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A191" s="2">
+        <v>2026</v>
+      </c>
       <c r="B191" s="2">
         <v>190</v>
       </c>
       <c r="C191" s="6">
         <v>73.099999999999994</v>
       </c>
-      <c r="D191" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="E191" s="7">
-        <v>83</v>
+      <c r="D191" s="12" t="s">
+        <v>1259</v>
+      </c>
+      <c r="E191" s="6">
+        <v>75</v>
       </c>
       <c r="F191" s="8">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="G191" s="2">
-        <v>60</v>
-      </c>
-      <c r="H191" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="I191" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="J191" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="K191" s="2" t="s">
-        <v>347</v>
+        <v>56</v>
+      </c>
+      <c r="H191" s="12" t="s">
+        <v>1264</v>
+      </c>
+      <c r="I191" s="12" t="s">
+        <v>1266</v>
+      </c>
+      <c r="J191" s="13" t="s">
+        <v>1272</v>
       </c>
       <c r="L191" s="2">
         <f>(SUM(7*E191,G191,2*F191))/10</f>
-        <v>77.099999999999994</v>
+        <v>70.099999999999994</v>
       </c>
     </row>
     <row r="192" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -12945,32 +12948,35 @@
         <v>191</v>
       </c>
       <c r="C192" s="6">
-        <v>73</v>
+        <v>73.099999999999994</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="E192" s="6">
-        <v>75</v>
-      </c>
-      <c r="F192" s="5">
-        <v>91</v>
-      </c>
-      <c r="G192" s="7">
+        <v>345</v>
+      </c>
+      <c r="E192" s="7">
         <v>83</v>
       </c>
+      <c r="F192" s="8">
+        <v>65</v>
+      </c>
+      <c r="G192" s="2">
+        <v>60</v>
+      </c>
       <c r="H192" s="2" t="s">
-        <v>31</v>
+        <v>346</v>
       </c>
       <c r="I192" s="2" t="s">
-        <v>41</v>
+        <v>177</v>
       </c>
       <c r="J192" s="3" t="s">
         <v>42</v>
       </c>
+      <c r="K192" s="2" t="s">
+        <v>347</v>
+      </c>
       <c r="L192" s="2">
         <f>(SUM(7*E192,G192,2*F192))/10</f>
-        <v>79</v>
+        <v>77.099999999999994</v>
       </c>
     </row>
     <row r="193" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -12981,32 +12987,29 @@
         <v>73</v>
       </c>
       <c r="D193" s="2" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E193" s="6">
-        <v>76</v>
-      </c>
-      <c r="F193" s="2">
-        <v>52</v>
-      </c>
-      <c r="G193" s="2">
-        <v>49</v>
+        <v>75</v>
+      </c>
+      <c r="F193" s="5">
+        <v>91</v>
+      </c>
+      <c r="G193" s="7">
+        <v>83</v>
       </c>
       <c r="H193" s="2" t="s">
-        <v>135</v>
+        <v>31</v>
       </c>
       <c r="I193" s="2" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="J193" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="K193" s="2" t="s">
-        <v>314</v>
+        <v>42</v>
       </c>
       <c r="L193" s="2">
         <f>(SUM(7*E193,G193,2*F193))/10</f>
-        <v>68.5</v>
+        <v>79</v>
       </c>
     </row>
     <row r="194" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -13017,28 +13020,28 @@
         <v>73</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E194" s="6">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="F194" s="2">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G194" s="2">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="H194" s="2" t="s">
-        <v>48</v>
+        <v>135</v>
       </c>
       <c r="I194" s="2" t="s">
-        <v>316</v>
+        <v>36</v>
       </c>
       <c r="J194" s="3" t="s">
         <v>32</v>
       </c>
       <c r="K194" s="2" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="L194" s="2">
         <f>(SUM(7*E194,G194,2*F194))/10</f>
@@ -13046,9 +13049,6 @@
       </c>
     </row>
     <row r="195" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A195" s="2">
-        <v>2026</v>
-      </c>
       <c r="B195" s="2">
         <v>194</v>
       </c>
@@ -13056,29 +13056,32 @@
         <v>73</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>1526</v>
+        <v>315</v>
       </c>
       <c r="E195" s="6">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="F195" s="2">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="G195" s="2">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="H195" s="2" t="s">
-        <v>1492</v>
+        <v>48</v>
       </c>
       <c r="I195" s="2" t="s">
-        <v>36</v>
+        <v>316</v>
       </c>
       <c r="J195" s="3" t="s">
-        <v>1547</v>
+        <v>32</v>
+      </c>
+      <c r="K195" s="2" t="s">
+        <v>317</v>
       </c>
       <c r="L195" s="2">
         <f>(SUM(7*E195,G195,2*F195))/10</f>
-        <v>67.5</v>
+        <v>68.5</v>
       </c>
     </row>
     <row r="196" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -13092,7 +13095,7 @@
         <v>73</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>1565</v>
+        <v>1526</v>
       </c>
       <c r="E196" s="6">
         <v>73</v>
@@ -13101,56 +13104,59 @@
         <v>56</v>
       </c>
       <c r="G196" s="2">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="H196" s="2" t="s">
-        <v>1574</v>
+        <v>1492</v>
       </c>
       <c r="I196" s="2" t="s">
         <v>36</v>
       </c>
       <c r="J196" s="3" t="s">
-        <v>1584</v>
-      </c>
-      <c r="K196" s="2" t="s">
-        <v>1570</v>
+        <v>1547</v>
       </c>
       <c r="L196" s="2">
         <f>(SUM(7*E196,G196,2*F196))/10</f>
-        <v>66.5</v>
+        <v>67.5</v>
       </c>
     </row>
     <row r="197" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A197" s="2">
+        <v>2026</v>
+      </c>
       <c r="B197" s="2">
         <v>196</v>
       </c>
       <c r="C197" s="6">
-        <v>72.900000000000006</v>
+        <v>73</v>
       </c>
       <c r="D197" s="2" t="s">
-        <v>318</v>
+        <v>1565</v>
       </c>
       <c r="E197" s="6">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F197" s="2">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G197" s="2">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="H197" s="2" t="s">
-        <v>104</v>
+        <v>1574</v>
       </c>
       <c r="I197" s="2" t="s">
         <v>36</v>
       </c>
       <c r="J197" s="3" t="s">
-        <v>132</v>
+        <v>1584</v>
+      </c>
+      <c r="K197" s="2" t="s">
+        <v>1570</v>
       </c>
       <c r="L197" s="2">
         <f>(SUM(7*E197,G197,2*F197))/10</f>
-        <v>67.900000000000006</v>
+        <v>66.5</v>
       </c>
     </row>
     <row r="198" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -13161,29 +13167,29 @@
         <v>72.900000000000006</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="E198" s="6">
-        <v>74</v>
-      </c>
-      <c r="F198" s="8">
-        <v>60</v>
-      </c>
-      <c r="G198" s="8">
-        <v>66</v>
+        <v>75</v>
+      </c>
+      <c r="F198" s="2">
+        <v>53</v>
+      </c>
+      <c r="G198" s="2">
+        <v>48</v>
       </c>
       <c r="H198" s="2" t="s">
-        <v>61</v>
+        <v>104</v>
       </c>
       <c r="I198" s="2" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="J198" s="3" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="L198" s="2">
         <f>(SUM(7*E198,G198,2*F198))/10</f>
-        <v>70.400000000000006</v>
+        <v>67.900000000000006</v>
       </c>
     </row>
     <row r="199" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -13194,22 +13200,22 @@
         <v>72.900000000000006</v>
       </c>
       <c r="D199" s="2" t="s">
-        <v>441</v>
+        <v>319</v>
       </c>
       <c r="E199" s="6">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F199" s="8">
-        <v>63</v>
-      </c>
-      <c r="G199" s="2">
-        <v>53</v>
+        <v>60</v>
+      </c>
+      <c r="G199" s="8">
+        <v>66</v>
       </c>
       <c r="H199" s="2" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="I199" s="2" t="s">
-        <v>177</v>
+        <v>22</v>
       </c>
       <c r="J199" s="3" t="s">
         <v>122</v>
@@ -13220,9 +13226,6 @@
       </c>
     </row>
     <row r="200" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A200" s="2">
-        <v>2026</v>
-      </c>
       <c r="B200" s="2">
         <v>199</v>
       </c>
@@ -13230,62 +13233,65 @@
         <v>72.900000000000006</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>1423</v>
+        <v>441</v>
       </c>
       <c r="E200" s="6">
-        <v>74</v>
-      </c>
-      <c r="F200" s="2">
-        <v>57</v>
-      </c>
-      <c r="G200" s="8">
-        <v>62</v>
+        <v>75</v>
+      </c>
+      <c r="F200" s="8">
+        <v>63</v>
+      </c>
+      <c r="G200" s="2">
+        <v>53</v>
       </c>
       <c r="H200" s="2" t="s">
-        <v>1430</v>
+        <v>48</v>
       </c>
       <c r="I200" s="2" t="s">
-        <v>36</v>
+        <v>177</v>
       </c>
       <c r="J200" s="3" t="s">
-        <v>1436</v>
+        <v>122</v>
       </c>
       <c r="L200" s="2">
         <f>(SUM(7*E200,G200,2*F200))/10</f>
-        <v>69.400000000000006</v>
+        <v>70.400000000000006</v>
       </c>
     </row>
     <row r="201" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A201" s="2">
+        <v>2026</v>
+      </c>
       <c r="B201" s="2">
         <v>200</v>
       </c>
       <c r="C201" s="6">
-        <v>72.8</v>
+        <v>72.900000000000006</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>320</v>
+        <v>1423</v>
       </c>
       <c r="E201" s="6">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F201" s="2">
-        <v>52</v>
-      </c>
-      <c r="G201" s="2">
-        <v>54</v>
+        <v>57</v>
+      </c>
+      <c r="G201" s="8">
+        <v>62</v>
       </c>
       <c r="H201" s="2" t="s">
-        <v>104</v>
+        <v>1430</v>
       </c>
       <c r="I201" s="2" t="s">
         <v>36</v>
       </c>
       <c r="J201" s="3" t="s">
-        <v>146</v>
+        <v>1436</v>
       </c>
       <c r="L201" s="2">
         <f>(SUM(7*E201,G201,2*F201))/10</f>
-        <v>68.3</v>
+        <v>69.400000000000006</v>
       </c>
     </row>
     <row r="202" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -13296,29 +13302,29 @@
         <v>72.8</v>
       </c>
       <c r="D202" s="2" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E202" s="6">
-        <v>77</v>
-      </c>
-      <c r="F202" s="6">
-        <v>76</v>
-      </c>
-      <c r="G202" s="7">
-        <v>87</v>
+        <v>75</v>
+      </c>
+      <c r="F202" s="2">
+        <v>52</v>
+      </c>
+      <c r="G202" s="2">
+        <v>54</v>
       </c>
       <c r="H202" s="2" t="s">
-        <v>322</v>
+        <v>104</v>
       </c>
       <c r="I202" s="2" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="J202" s="3" t="s">
-        <v>42</v>
+        <v>146</v>
       </c>
       <c r="L202" s="2">
         <f>(SUM(7*E202,G202,2*F202))/10</f>
-        <v>77.8</v>
+        <v>68.3</v>
       </c>
     </row>
     <row r="203" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -13326,35 +13332,32 @@
         <v>202</v>
       </c>
       <c r="C203" s="6">
-        <v>72.599999999999994</v>
+        <v>72.8</v>
       </c>
       <c r="D203" s="2" t="s">
-        <v>170</v>
+        <v>321</v>
       </c>
       <c r="E203" s="6">
+        <v>77</v>
+      </c>
+      <c r="F203" s="6">
         <v>76</v>
       </c>
-      <c r="F203" s="8">
-        <v>61</v>
-      </c>
-      <c r="G203" s="2">
-        <v>52</v>
+      <c r="G203" s="7">
+        <v>87</v>
       </c>
       <c r="H203" s="2" t="s">
-        <v>171</v>
+        <v>322</v>
       </c>
       <c r="I203" s="2" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="J203" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="K203" s="2" t="s">
-        <v>172</v>
+        <v>42</v>
       </c>
       <c r="L203" s="2">
         <f>(SUM(7*E203,G203,2*F203))/10</f>
-        <v>70.599999999999994</v>
+        <v>77.8</v>
       </c>
     </row>
     <row r="204" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -13365,29 +13368,32 @@
         <v>72.599999999999994</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>323</v>
+        <v>170</v>
       </c>
       <c r="E204" s="6">
-        <v>73</v>
-      </c>
-      <c r="F204" s="5">
-        <v>94</v>
-      </c>
-      <c r="G204" s="7">
-        <v>87</v>
+        <v>76</v>
+      </c>
+      <c r="F204" s="8">
+        <v>61</v>
+      </c>
+      <c r="G204" s="2">
+        <v>52</v>
       </c>
       <c r="H204" s="2" t="s">
-        <v>324</v>
+        <v>171</v>
       </c>
       <c r="I204" s="2" t="s">
-        <v>325</v>
+        <v>41</v>
       </c>
       <c r="J204" s="3" t="s">
-        <v>42</v>
+        <v>140</v>
+      </c>
+      <c r="K204" s="2" t="s">
+        <v>172</v>
       </c>
       <c r="L204" s="2">
         <f>(SUM(7*E204,G204,2*F204))/10</f>
-        <v>78.599999999999994</v>
+        <v>70.599999999999994</v>
       </c>
     </row>
     <row r="205" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -13398,29 +13404,29 @@
         <v>72.599999999999994</v>
       </c>
       <c r="D205" s="2" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="E205" s="6">
-        <v>75</v>
-      </c>
-      <c r="F205" s="6">
-        <v>75</v>
-      </c>
-      <c r="G205" s="8">
-        <v>66</v>
+        <v>73</v>
+      </c>
+      <c r="F205" s="5">
+        <v>94</v>
+      </c>
+      <c r="G205" s="7">
+        <v>87</v>
       </c>
       <c r="H205" s="2" t="s">
-        <v>291</v>
+        <v>324</v>
       </c>
       <c r="I205" s="2" t="s">
-        <v>13</v>
+        <v>325</v>
       </c>
       <c r="J205" s="3" t="s">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="L205" s="2">
         <f>(SUM(7*E205,G205,2*F205))/10</f>
-        <v>74.099999999999994</v>
+        <v>78.599999999999994</v>
       </c>
     </row>
     <row r="206" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -13431,35 +13437,32 @@
         <v>72.599999999999994</v>
       </c>
       <c r="D206" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E206" s="6">
-        <v>74</v>
-      </c>
-      <c r="F206" s="8">
-        <v>65</v>
-      </c>
-      <c r="G206" s="2">
-        <v>53</v>
+        <v>75</v>
+      </c>
+      <c r="F206" s="6">
+        <v>75</v>
+      </c>
+      <c r="G206" s="8">
+        <v>66</v>
       </c>
       <c r="H206" s="2" t="s">
-        <v>61</v>
+        <v>291</v>
       </c>
       <c r="I206" s="2" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="J206" s="3" t="s">
-        <v>122</v>
+        <v>14</v>
       </c>
       <c r="L206" s="2">
         <f>(SUM(7*E206,G206,2*F206))/10</f>
-        <v>70.099999999999994</v>
+        <v>74.099999999999994</v>
       </c>
     </row>
     <row r="207" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A207" s="2">
-        <v>2026</v>
-      </c>
       <c r="B207" s="2">
         <v>206</v>
       </c>
@@ -13467,65 +13470,68 @@
         <v>72.599999999999994</v>
       </c>
       <c r="D207" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E207" s="6">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="F207" s="8">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="G207" s="2">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="H207" s="2" t="s">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="I207" s="2" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="J207" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="K207" s="2" t="s">
-        <v>329</v>
-      </c>
       <c r="L207" s="2">
         <f>(SUM(7*E207,G207,2*F207))/10</f>
-        <v>69.099999999999994</v>
+        <v>70.099999999999994</v>
       </c>
     </row>
     <row r="208" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A208" s="2">
+        <v>2026</v>
+      </c>
       <c r="B208" s="2">
         <v>207</v>
       </c>
       <c r="C208" s="6">
-        <v>72.5</v>
+        <v>72.599999999999994</v>
       </c>
       <c r="D208" s="2" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="E208" s="6">
-        <v>73</v>
-      </c>
-      <c r="F208" s="2">
+        <v>71</v>
+      </c>
+      <c r="F208" s="8">
+        <v>68</v>
+      </c>
+      <c r="G208" s="2">
         <v>58</v>
       </c>
-      <c r="G208" s="2">
-        <v>53</v>
-      </c>
       <c r="H208" s="2" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="I208" s="2" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="J208" s="3" t="s">
-        <v>146</v>
+        <v>122</v>
+      </c>
+      <c r="K208" s="2" t="s">
+        <v>329</v>
       </c>
       <c r="L208" s="2">
         <f>(SUM(7*E208,G208,2*F208))/10</f>
-        <v>68</v>
+        <v>69.099999999999994</v>
       </c>
     </row>
     <row r="209" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -13536,29 +13542,29 @@
         <v>72.5</v>
       </c>
       <c r="D209" s="2" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E209" s="6">
-        <v>70</v>
-      </c>
-      <c r="F209" s="6">
-        <v>77</v>
-      </c>
-      <c r="G209" s="6">
-        <v>71</v>
+        <v>73</v>
+      </c>
+      <c r="F209" s="2">
+        <v>58</v>
+      </c>
+      <c r="G209" s="2">
+        <v>53</v>
       </c>
       <c r="H209" s="2" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="I209" s="2" t="s">
-        <v>332</v>
+        <v>41</v>
       </c>
       <c r="J209" s="3" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="L209" s="2">
         <f>(SUM(7*E209,G209,2*F209))/10</f>
-        <v>71.5</v>
+        <v>68</v>
       </c>
     </row>
     <row r="210" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -13569,29 +13575,29 @@
         <v>72.5</v>
       </c>
       <c r="D210" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E210" s="6">
-        <v>72</v>
-      </c>
-      <c r="F210" s="8">
-        <v>60</v>
-      </c>
-      <c r="G210" s="8">
-        <v>66</v>
+        <v>70</v>
+      </c>
+      <c r="F210" s="6">
+        <v>77</v>
+      </c>
+      <c r="G210" s="6">
+        <v>71</v>
       </c>
       <c r="H210" s="2" t="s">
-        <v>145</v>
+        <v>48</v>
       </c>
       <c r="I210" s="2" t="s">
-        <v>13</v>
+        <v>332</v>
       </c>
       <c r="J210" s="3" t="s">
-        <v>32</v>
+        <v>140</v>
       </c>
       <c r="L210" s="2">
         <f>(SUM(7*E210,G210,2*F210))/10</f>
-        <v>69</v>
+        <v>71.5</v>
       </c>
     </row>
     <row r="211" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -13602,35 +13608,32 @@
         <v>72.5</v>
       </c>
       <c r="D211" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="E211" s="8">
-        <v>69</v>
-      </c>
-      <c r="F211" s="7">
-        <v>80</v>
-      </c>
-      <c r="G211" s="6">
+        <v>333</v>
+      </c>
+      <c r="E211" s="6">
         <v>72</v>
       </c>
+      <c r="F211" s="8">
+        <v>60</v>
+      </c>
+      <c r="G211" s="8">
+        <v>66</v>
+      </c>
       <c r="H211" s="2" t="s">
-        <v>256</v>
+        <v>145</v>
       </c>
       <c r="I211" s="2" t="s">
         <v>13</v>
       </c>
       <c r="J211" s="3" t="s">
-        <v>140</v>
+        <v>32</v>
       </c>
       <c r="L211" s="2">
         <f>(SUM(7*E211,G211,2*F211))/10</f>
-        <v>71.5</v>
+        <v>69</v>
       </c>
     </row>
     <row r="212" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A212" s="2">
-        <v>2026</v>
-      </c>
       <c r="B212" s="2">
         <v>211</v>
       </c>
@@ -13638,68 +13641,68 @@
         <v>72.5</v>
       </c>
       <c r="D212" s="2" t="s">
-        <v>1643</v>
-      </c>
-      <c r="E212" s="6">
-        <v>76</v>
-      </c>
-      <c r="F212" s="2">
-        <v>50</v>
-      </c>
-      <c r="G212" s="2">
-        <v>53</v>
+        <v>334</v>
+      </c>
+      <c r="E212" s="8">
+        <v>69</v>
+      </c>
+      <c r="F212" s="7">
+        <v>80</v>
+      </c>
+      <c r="G212" s="6">
+        <v>72</v>
       </c>
       <c r="H212" s="2" t="s">
-        <v>1653</v>
+        <v>256</v>
       </c>
       <c r="I212" s="2" t="s">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="J212" s="3" t="s">
-        <v>1665</v>
-      </c>
-      <c r="K212" s="2" t="s">
-        <v>1672</v>
+        <v>140</v>
       </c>
       <c r="L212" s="2">
         <f>(SUM(7*E212,G212,2*F212))/10</f>
-        <v>68.5</v>
+        <v>71.5</v>
       </c>
     </row>
     <row r="213" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A213" s="2">
+        <v>2026</v>
+      </c>
       <c r="B213" s="2">
         <v>212</v>
       </c>
       <c r="C213" s="6">
-        <v>72.400000000000006</v>
+        <v>72.5</v>
       </c>
       <c r="D213" s="2" t="s">
-        <v>335</v>
+        <v>1643</v>
       </c>
       <c r="E213" s="6">
         <v>76</v>
       </c>
       <c r="F213" s="2">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G213" s="2">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="H213" s="2" t="s">
-        <v>104</v>
+        <v>1653</v>
       </c>
       <c r="I213" s="2" t="s">
         <v>36</v>
       </c>
       <c r="J213" s="3" t="s">
-        <v>132</v>
+        <v>1665</v>
       </c>
       <c r="K213" s="2" t="s">
-        <v>336</v>
+        <v>1672</v>
       </c>
       <c r="L213" s="2">
         <f>(SUM(7*E213,G213,2*F213))/10</f>
-        <v>66.400000000000006</v>
+        <v>68.5</v>
       </c>
     </row>
     <row r="214" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -13710,29 +13713,32 @@
         <v>72.400000000000006</v>
       </c>
       <c r="D214" s="2" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="E214" s="6">
-        <v>70</v>
-      </c>
-      <c r="F214" s="6">
-        <v>75</v>
-      </c>
-      <c r="G214" s="6">
-        <v>74</v>
+        <v>76</v>
+      </c>
+      <c r="F214" s="2">
+        <v>51</v>
+      </c>
+      <c r="G214" s="2">
+        <v>30</v>
       </c>
       <c r="H214" s="2" t="s">
-        <v>48</v>
+        <v>104</v>
       </c>
       <c r="I214" s="2" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="J214" s="3" t="s">
-        <v>140</v>
+        <v>132</v>
+      </c>
+      <c r="K214" s="2" t="s">
+        <v>336</v>
       </c>
       <c r="L214" s="2">
         <f>(SUM(7*E214,G214,2*F214))/10</f>
-        <v>71.400000000000006</v>
+        <v>66.400000000000006</v>
       </c>
     </row>
     <row r="215" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -13743,29 +13749,29 @@
         <v>72.400000000000006</v>
       </c>
       <c r="D215" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="E215" s="8">
-        <v>67</v>
-      </c>
-      <c r="F215" s="8">
-        <v>68</v>
-      </c>
-      <c r="G215" s="8">
-        <v>69</v>
+        <v>337</v>
+      </c>
+      <c r="E215" s="6">
+        <v>70</v>
+      </c>
+      <c r="F215" s="6">
+        <v>75</v>
+      </c>
+      <c r="G215" s="6">
+        <v>74</v>
       </c>
       <c r="H215" s="2" t="s">
-        <v>339</v>
+        <v>48</v>
       </c>
       <c r="I215" s="2" t="s">
-        <v>298</v>
+        <v>41</v>
       </c>
       <c r="J215" s="3" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="L215" s="2">
         <f>(SUM(7*E215,G215,2*F215))/10</f>
-        <v>67.400000000000006</v>
+        <v>71.400000000000006</v>
       </c>
     </row>
     <row r="216" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -13776,32 +13782,29 @@
         <v>72.400000000000006</v>
       </c>
       <c r="D216" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="E216" s="6">
-        <v>72</v>
-      </c>
-      <c r="F216" s="2">
-        <v>55</v>
-      </c>
-      <c r="G216" s="2">
-        <v>55</v>
+        <v>338</v>
+      </c>
+      <c r="E216" s="8">
+        <v>67</v>
+      </c>
+      <c r="F216" s="8">
+        <v>68</v>
+      </c>
+      <c r="G216" s="8">
+        <v>69</v>
       </c>
       <c r="H216" s="2" t="s">
-        <v>48</v>
+        <v>339</v>
       </c>
       <c r="I216" s="2" t="s">
-        <v>218</v>
+        <v>298</v>
       </c>
       <c r="J216" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="K216" s="2" t="s">
-        <v>341</v>
+        <v>132</v>
       </c>
       <c r="L216" s="2">
         <f>(SUM(7*E216,G216,2*F216))/10</f>
-        <v>66.900000000000006</v>
+        <v>67.400000000000006</v>
       </c>
     </row>
     <row r="217" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -13812,29 +13815,32 @@
         <v>72.400000000000006</v>
       </c>
       <c r="D217" s="2" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="E217" s="6">
-        <v>71</v>
-      </c>
-      <c r="F217" s="8">
-        <v>63</v>
-      </c>
-      <c r="G217" s="6">
-        <v>76</v>
+        <v>72</v>
+      </c>
+      <c r="F217" s="2">
+        <v>55</v>
+      </c>
+      <c r="G217" s="2">
+        <v>55</v>
       </c>
       <c r="H217" s="2" t="s">
-        <v>145</v>
+        <v>48</v>
       </c>
       <c r="I217" s="2" t="s">
-        <v>13</v>
+        <v>218</v>
       </c>
       <c r="J217" s="3" t="s">
-        <v>18</v>
+        <v>32</v>
+      </c>
+      <c r="K217" s="2" t="s">
+        <v>341</v>
       </c>
       <c r="L217" s="2">
         <f>(SUM(7*E217,G217,2*F217))/10</f>
-        <v>69.900000000000006</v>
+        <v>66.900000000000006</v>
       </c>
     </row>
     <row r="218" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -13845,71 +13851,65 @@
         <v>72.400000000000006</v>
       </c>
       <c r="D218" s="2" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E218" s="6">
-        <v>75</v>
-      </c>
-      <c r="F218" s="2">
-        <v>52</v>
-      </c>
-      <c r="G218" s="2">
-        <v>40</v>
+        <v>71</v>
+      </c>
+      <c r="F218" s="8">
+        <v>63</v>
+      </c>
+      <c r="G218" s="6">
+        <v>76</v>
       </c>
       <c r="H218" s="2" t="s">
-        <v>217</v>
+        <v>145</v>
       </c>
       <c r="I218" s="2" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="J218" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="K218" s="2" t="s">
-        <v>344</v>
+        <v>18</v>
       </c>
       <c r="L218" s="2">
         <f>(SUM(7*E218,G218,2*F218))/10</f>
-        <v>66.900000000000006</v>
+        <v>69.900000000000006</v>
       </c>
     </row>
     <row r="219" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A219" s="2">
-        <v>2026</v>
-      </c>
       <c r="B219" s="2">
         <v>218</v>
       </c>
       <c r="C219" s="6">
         <v>72.400000000000006</v>
       </c>
-      <c r="D219" s="12" t="s">
-        <v>1322</v>
+      <c r="D219" s="2" t="s">
+        <v>343</v>
       </c>
       <c r="E219" s="6">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F219" s="2">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="G219" s="2">
-        <v>44</v>
-      </c>
-      <c r="H219" s="12" t="s">
-        <v>1264</v>
+        <v>40</v>
+      </c>
+      <c r="H219" s="2" t="s">
+        <v>217</v>
       </c>
       <c r="I219" s="2" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="J219" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="K219" s="12" t="s">
-        <v>1326</v>
+        <v>146</v>
+      </c>
+      <c r="K219" s="2" t="s">
+        <v>344</v>
       </c>
       <c r="L219" s="2">
         <f>(SUM(7*E219,G219,2*F219))/10</f>
-        <v>66.400000000000006</v>
+        <v>66.900000000000006</v>
       </c>
     </row>
     <row r="220" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -46103,8 +46103,8 @@
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L1210">
-    <sortCondition descending="1" ref="C2:C1210"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L1208">
+    <sortCondition descending="1" ref="C2:C1208"/>
   </sortState>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
